--- a/metadatalocation.xlsx
+++ b/metadatalocation.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alexis/dialects_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alexis/02_Projects/dialects_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C4CE440-1A76-EE43-B1BD-06BAD2154467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A344638-67B0-EC48-84BC-4C0ADFA7FD16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19420" yWindow="1780" windowWidth="13520" windowHeight="16940" xr2:uid="{7A5E0C24-EC50-BF4E-A0C6-90F8CD4A6738}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>Beijing</t>
   </si>
@@ -77,6 +77,24 @@
   </si>
   <si>
     <t>Wenzhou</t>
+  </si>
+  <si>
+    <t>Kunming</t>
+  </si>
+  <si>
+    <t>Lanzhou</t>
+  </si>
+  <si>
+    <t>Pingyao</t>
+  </si>
+  <si>
+    <t>Shanghai</t>
+  </si>
+  <si>
+    <t>Shantou</t>
+  </si>
+  <si>
+    <t>Tianjin</t>
   </si>
 </sst>
 </file>
@@ -937,7 +955,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66916B8D-182A-3345-A367-092950833031}">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -1135,6 +1153,72 @@
         <v>120.647919</v>
       </c>
     </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19">
+        <v>24.880095000000001</v>
+      </c>
+      <c r="C19">
+        <v>102.832893</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20">
+        <v>36.057968000000002</v>
+      </c>
+      <c r="C20">
+        <v>103.790047</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21">
+        <v>30.402470000000001</v>
+      </c>
+      <c r="C21">
+        <v>119.945663</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22">
+        <v>31.230391000000001</v>
+      </c>
+      <c r="C22">
+        <v>121.47370100000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23">
+        <v>23.360821000000001</v>
+      </c>
+      <c r="C23">
+        <v>116.67749000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24">
+        <v>39.343356999999997</v>
+      </c>
+      <c r="C24">
+        <v>117.361649</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
